--- a/ky/downloads/data-excel/1.5.1.xlsx
+++ b/ky/downloads/data-excel/1.5.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1C8F37-4E69-4F40-AC3A-DED9F87303DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13500" windowHeight="9810"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="49">
   <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
@@ -185,7 +186,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -314,7 +315,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -322,30 +323,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -353,75 +351,51 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal 17" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="5"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 7" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -437,7 +411,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -8163,16 +8137,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35.140625" customWidth="1"/>
     <col min="4" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -8182,18 +8156,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -8214,8 +8188,9 @@
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
@@ -8240,44 +8215,47 @@
       <c r="H4" s="11">
         <v>2011</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>2012</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>2013</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>2014</v>
       </c>
       <c r="L4" s="11">
         <v>2015</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <v>2016</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>2017</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="11">
         <v>2018</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
         <v>2019</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="11">
         <v>2020</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <v>2021</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="11">
         <v>2022</v>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="11">
         <v>2023</v>
       </c>
+      <c r="U4" s="11">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -8287,60 +8265,63 @@
       <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>93</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>281</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>71</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>158</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>140</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>99</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>95</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>62</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>53</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <v>47</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <v>141</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="12">
         <v>18</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="12">
         <v>17</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="12">
         <v>51</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="12">
         <v>109</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="12">
         <v>135</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="12">
         <v>44</v>
       </c>
+      <c r="U5" s="12">
+        <v>79</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -8349,184 +8330,193 @@
       <c r="C6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="16">
         <v>74</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="17">
         <v>184</v>
       </c>
-      <c r="F6" s="20">
-        <v>48</v>
-      </c>
-      <c r="G6" s="18">
+      <c r="F6" s="18">
+        <v>48</v>
+      </c>
+      <c r="G6" s="16">
         <v>106</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="17">
         <v>93</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="18">
         <v>65</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="16">
         <v>62</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="17">
         <v>39</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="18">
         <v>33</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M6" s="16">
         <v>37</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="17">
         <v>85</v>
       </c>
-      <c r="O6" s="20">
+      <c r="O6" s="18">
         <v>14</v>
       </c>
-      <c r="P6" s="20">
+      <c r="P6" s="18">
         <v>8</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="Q6" s="18">
         <v>29</v>
       </c>
-      <c r="R6" s="20">
+      <c r="R6" s="18">
         <v>74</v>
       </c>
-      <c r="S6" s="20">
+      <c r="S6" s="18">
         <v>99</v>
       </c>
-      <c r="T6" s="20">
+      <c r="T6" s="18">
         <v>24</v>
       </c>
+      <c r="U6" s="18">
+        <v>52</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="16">
         <v>19</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="17">
         <v>97</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="18">
         <v>23</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="16">
         <v>52</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="17">
         <v>47</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="18">
         <v>34</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="16">
         <v>33</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="17">
         <v>23</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="18">
         <v>20</v>
       </c>
-      <c r="M7" s="18">
+      <c r="M7" s="16">
         <v>10</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="17">
         <v>56</v>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="18">
         <v>4</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="18">
         <v>9</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="Q7" s="18">
         <v>22</v>
       </c>
-      <c r="R7" s="21">
+      <c r="R7" s="18">
         <v>35</v>
       </c>
-      <c r="S7" s="21">
+      <c r="S7" s="18">
         <v>36</v>
       </c>
-      <c r="T7" s="21">
+      <c r="T7" s="18">
         <v>20</v>
       </c>
+      <c r="U7" s="18">
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+    <row r="8" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="23">
         <v>8</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="24">
         <v>9</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="29">
+      <c r="F8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="23">
         <v>15</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="24">
         <v>7</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="24">
         <v>9</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="23">
         <v>3</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="24">
         <v>3</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="24">
         <v>1</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="23">
         <v>9</v>
       </c>
-      <c r="N8" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="P8" s="31">
+      <c r="N8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="P8" s="24">
         <v>6</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="24">
         <v>5</v>
       </c>
-      <c r="R8" s="31">
+      <c r="R8" s="24">
         <v>36</v>
       </c>
-      <c r="S8" s="31">
+      <c r="S8" s="24">
         <v>97</v>
       </c>
-      <c r="T8" s="31" t="s">
-        <v>48</v>
+      <c r="T8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="U8" s="24">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -8535,121 +8525,127 @@
       <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="16">
         <v>6</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="17">
         <v>9</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="F9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="16">
         <v>11</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="17">
         <v>4</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="18">
         <v>7</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="16">
         <v>3</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="17">
         <v>3</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="18">
         <v>1</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="16">
         <v>7</v>
       </c>
-      <c r="N9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="20">
+      <c r="N9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9" s="18">
         <v>4</v>
       </c>
-      <c r="Q9" s="20">
+      <c r="Q9" s="18">
         <v>3</v>
       </c>
-      <c r="R9" s="20">
+      <c r="R9" s="18">
         <v>35</v>
       </c>
-      <c r="S9" s="20">
+      <c r="S9" s="18">
         <v>80</v>
       </c>
-      <c r="T9" s="20" t="s">
-        <v>48</v>
+      <c r="T9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="U9" s="18">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="16">
         <v>2</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="18">
+      <c r="E10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="16">
         <v>4</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="17">
         <v>3</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="18">
         <v>2</v>
       </c>
-      <c r="J10" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="18">
+      <c r="J10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="16">
         <v>2</v>
       </c>
-      <c r="N10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P10" s="21">
+      <c r="N10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P10" s="18">
         <v>2</v>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="18">
         <v>2</v>
       </c>
-      <c r="R10" s="21">
+      <c r="R10" s="18">
         <v>1</v>
       </c>
-      <c r="S10" s="21">
+      <c r="S10" s="18">
         <v>17</v>
       </c>
-      <c r="T10" s="21" t="s">
+      <c r="T10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="U10" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -8659,60 +8655,63 @@
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="23">
         <v>5</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="24">
         <v>25</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="12">
         <v>39</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="23">
         <v>32</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="24">
         <v>35</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="12">
         <v>33</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="23">
         <v>31</v>
       </c>
-      <c r="K11" s="30">
+      <c r="K11" s="24">
         <v>17</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="12">
         <v>11</v>
       </c>
-      <c r="M11" s="33">
+      <c r="M11" s="23">
         <v>13</v>
       </c>
-      <c r="N11" s="30">
+      <c r="N11" s="24">
         <v>43</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="12">
         <v>4</v>
       </c>
-      <c r="P11" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="34">
+      <c r="P11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="12">
         <v>15</v>
       </c>
-      <c r="R11" s="34">
+      <c r="R11" s="12">
         <v>15</v>
       </c>
-      <c r="S11" s="34">
+      <c r="S11" s="12">
         <v>17</v>
       </c>
-      <c r="T11" s="34">
+      <c r="T11" s="12">
         <v>5</v>
       </c>
+      <c r="U11" s="12">
+        <v>24</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -8721,121 +8720,127 @@
       <c r="C12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="16">
         <v>5</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="17">
         <v>18</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="18">
         <v>27</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="16">
         <v>21</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="17">
         <v>27</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="18">
         <v>17</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="16">
         <v>22</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="17">
         <v>11</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="18">
         <v>5</v>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="16">
         <v>9</v>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="17">
         <v>29</v>
       </c>
-      <c r="O12" s="20">
+      <c r="O12" s="18">
         <v>4</v>
       </c>
-      <c r="P12" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q12" s="20">
+      <c r="P12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q12" s="18">
         <v>9</v>
       </c>
-      <c r="R12" s="20">
+      <c r="R12" s="18">
         <v>8</v>
       </c>
-      <c r="S12" s="20">
+      <c r="S12" s="18">
         <v>11</v>
       </c>
-      <c r="T12" s="20">
+      <c r="T12" s="18">
         <v>1</v>
       </c>
+      <c r="U12" s="18">
+        <v>21</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="19">
+      <c r="D13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="17">
         <v>7</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="18">
         <v>12</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="16">
         <v>11</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="17">
         <v>8</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="18">
         <v>16</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="16">
         <v>9</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="17">
         <v>6</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="18">
         <v>6</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="16">
         <v>4</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="17">
         <v>14</v>
       </c>
-      <c r="O13" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P13" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="21">
+      <c r="O13" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" s="18">
         <v>6</v>
       </c>
-      <c r="R13" s="21">
+      <c r="R13" s="18">
         <v>7</v>
       </c>
-      <c r="S13" s="21">
+      <c r="S13" s="18">
         <v>6</v>
       </c>
-      <c r="T13" s="21">
+      <c r="T13" s="18">
         <v>4</v>
       </c>
+      <c r="U13" s="18">
+        <v>3</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -8845,60 +8850,63 @@
       <c r="C14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="23">
         <v>14</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="24">
         <v>42</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="12">
         <v>11</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="23">
         <v>15</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="24">
         <v>17</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="12">
         <v>4</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="23">
         <v>21</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="24">
         <v>25</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="12">
         <v>6</v>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="23">
         <v>2</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="24">
         <v>6</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="12">
         <v>2</v>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="12">
         <v>5</v>
       </c>
-      <c r="Q14" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="R14" s="34">
+      <c r="Q14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" s="12">
         <v>12</v>
       </c>
-      <c r="S14" s="34">
+      <c r="S14" s="12">
         <v>5</v>
       </c>
-      <c r="T14" s="34">
+      <c r="T14" s="12">
         <v>8</v>
       </c>
+      <c r="U14" s="12">
+        <v>12</v>
+      </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -8907,121 +8915,127 @@
       <c r="C15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="16">
         <v>10</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="17">
         <v>26</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="18">
         <v>7</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="16">
         <v>10</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="17">
         <v>9</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="18">
         <v>4</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="16">
         <v>13</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="17">
         <v>16</v>
       </c>
-      <c r="L15" s="20">
+      <c r="L15" s="18">
         <v>5</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="16">
         <v>1</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="17">
         <v>6</v>
       </c>
-      <c r="O15" s="20">
+      <c r="O15" s="18">
         <v>1</v>
       </c>
-      <c r="P15" s="20">
+      <c r="P15" s="18">
         <v>2</v>
       </c>
-      <c r="Q15" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R15" s="20">
+      <c r="Q15" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R15" s="18">
         <v>7</v>
       </c>
-      <c r="S15" s="20">
+      <c r="S15" s="18">
         <v>3</v>
       </c>
-      <c r="T15" s="20">
+      <c r="T15" s="18">
         <v>6</v>
       </c>
+      <c r="U15" s="18">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="16">
         <v>4</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="17">
         <v>16</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="18">
         <v>4</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="16">
         <v>5</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="17">
         <v>8</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="18">
+      <c r="I16" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="16">
         <v>8</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="17">
         <v>9</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="18">
         <v>1</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="16">
         <v>1</v>
       </c>
-      <c r="N16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O16" s="21">
+      <c r="N16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O16" s="18">
         <v>1</v>
       </c>
-      <c r="P16" s="21">
+      <c r="P16" s="18">
         <v>3</v>
       </c>
-      <c r="Q16" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R16" s="21">
+      <c r="Q16" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R16" s="18">
         <v>5</v>
       </c>
-      <c r="S16" s="21">
+      <c r="S16" s="18">
         <v>2</v>
       </c>
-      <c r="T16" s="21">
+      <c r="T16" s="18">
         <v>2</v>
       </c>
+      <c r="U16" s="18">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -9031,60 +9045,63 @@
       <c r="C17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="23">
         <v>5</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="24">
         <v>6</v>
       </c>
-      <c r="F17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="33">
+      <c r="F17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="23">
         <v>7</v>
       </c>
-      <c r="H17" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="34">
+      <c r="H17" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="12">
         <v>5</v>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="23">
         <v>8</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="24">
         <v>2</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="12">
         <v>9</v>
       </c>
-      <c r="M17" s="33">
+      <c r="M17" s="23">
         <v>1</v>
       </c>
-      <c r="N17" s="30">
+      <c r="N17" s="24">
         <v>2</v>
       </c>
-      <c r="O17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="P17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="R17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="S17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="T17" s="34">
+      <c r="O17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T17" s="12">
         <v>5</v>
       </c>
+      <c r="U17" s="12" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -9093,121 +9110,127 @@
       <c r="C18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="16">
         <v>4</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="17">
         <v>4</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="18">
+      <c r="F18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="16">
         <v>4</v>
       </c>
-      <c r="H18" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="20">
+      <c r="H18" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="18">
         <v>4</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="16">
         <v>5</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="17">
         <v>2</v>
       </c>
-      <c r="L18" s="20">
+      <c r="L18" s="18">
         <v>6</v>
       </c>
-      <c r="M18" s="18">
+      <c r="M18" s="16">
         <v>1</v>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="17">
         <v>2</v>
       </c>
-      <c r="O18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="S18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" s="20">
+      <c r="O18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T18" s="18">
         <v>1</v>
       </c>
+      <c r="U18" s="18" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="17">
         <v>2</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="18">
+      <c r="F19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="16">
         <v>3</v>
       </c>
-      <c r="H19" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" s="21">
+      <c r="H19" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="18">
         <v>1</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="16">
         <v>3</v>
       </c>
-      <c r="K19" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L19" s="21">
+      <c r="K19" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="18">
         <v>3</v>
       </c>
-      <c r="M19" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N19" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="S19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="T19" s="21">
+      <c r="M19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S19" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T19" s="18">
         <v>4</v>
       </c>
+      <c r="U19" s="18" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="20" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
@@ -9217,60 +9240,63 @@
       <c r="C20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="23">
         <v>6</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="24">
         <v>96</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="12">
         <v>2</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="23">
         <v>19</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="24">
         <v>11</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="12">
         <v>22</v>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="23">
         <v>5</v>
       </c>
-      <c r="K20" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="L20" s="34">
+      <c r="K20" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="12">
         <v>10</v>
       </c>
-      <c r="M20" s="33">
+      <c r="M20" s="23">
         <v>1</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="24">
         <v>35</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="12">
         <v>1</v>
       </c>
-      <c r="P20" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q20" s="34">
+      <c r="P20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q20" s="12">
         <v>7</v>
       </c>
-      <c r="R20" s="34">
+      <c r="R20" s="12">
         <v>17</v>
       </c>
-      <c r="S20" s="34">
+      <c r="S20" s="12">
         <v>6</v>
       </c>
-      <c r="T20" s="34">
+      <c r="T20" s="12">
         <v>7</v>
       </c>
+      <c r="U20" s="12">
+        <v>16</v>
+      </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -9279,121 +9305,127 @@
       <c r="C21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="16">
         <v>6</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="17">
         <v>50</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="18">
         <v>2</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="16">
         <v>12</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="17">
         <v>6</v>
       </c>
-      <c r="I21" s="20">
+      <c r="I21" s="18">
         <v>16</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="16">
         <v>3</v>
       </c>
-      <c r="K21" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L21" s="20">
+      <c r="K21" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="18">
         <v>7</v>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="16">
         <v>1</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="17">
         <v>17</v>
       </c>
-      <c r="O21" s="20">
+      <c r="O21" s="18">
         <v>1</v>
       </c>
-      <c r="P21" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q21" s="20">
+      <c r="P21" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q21" s="18">
         <v>7</v>
       </c>
-      <c r="R21" s="20">
+      <c r="R21" s="18">
         <v>8</v>
       </c>
-      <c r="S21" s="20">
+      <c r="S21" s="18">
         <v>1</v>
       </c>
-      <c r="T21" s="20">
+      <c r="T21" s="18">
         <v>5</v>
       </c>
+      <c r="U21" s="18">
+        <v>10</v>
+      </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="19">
+      <c r="D22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="17">
         <v>46</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="18">
+      <c r="F22" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="16">
         <v>7</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="17">
         <v>5</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="18">
         <v>6</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="16">
         <v>2</v>
       </c>
-      <c r="K22" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L22" s="21">
+      <c r="K22" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="18">
         <v>3</v>
       </c>
-      <c r="M22" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N22" s="19">
+      <c r="M22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22" s="17">
         <v>18</v>
       </c>
-      <c r="O22" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P22" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R22" s="21">
+      <c r="O22" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q22" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R22" s="18">
         <v>9</v>
       </c>
-      <c r="S22" s="21">
+      <c r="S22" s="18">
         <v>5</v>
       </c>
-      <c r="T22" s="21">
+      <c r="T22" s="18">
         <v>2</v>
       </c>
+      <c r="U22" s="18">
+        <v>6</v>
+      </c>
     </row>
-    <row r="23" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
@@ -9403,60 +9435,63 @@
       <c r="C23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="23">
         <v>1</v>
       </c>
-      <c r="E23" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="33">
+      <c r="E23" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="23">
         <v>4</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="24">
         <v>6</v>
       </c>
-      <c r="I23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="J23" s="33">
+      <c r="I23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" s="23">
         <v>5</v>
       </c>
-      <c r="K23" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="L23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="M23" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="N23" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="O23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="P23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="R23" s="34">
+      <c r="K23" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="N23" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R23" s="12">
         <v>9</v>
       </c>
-      <c r="S23" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="T23" s="34" t="s">
+      <c r="S23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -9465,121 +9500,127 @@
       <c r="C24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="16">
         <v>1</v>
       </c>
-      <c r="E24" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="18">
+      <c r="E24" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="16">
         <v>3</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="17">
         <v>4</v>
       </c>
-      <c r="I24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J24" s="18">
+      <c r="I24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="16">
         <v>4</v>
       </c>
-      <c r="K24" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N24" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R24" s="20">
+      <c r="K24" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R24" s="18">
         <v>7</v>
       </c>
-      <c r="S24" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="T24" s="20" t="s">
+      <c r="S24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="U24" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="18">
+      <c r="D25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="16">
         <v>1</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="17">
         <v>2</v>
       </c>
-      <c r="I25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="J25" s="18">
+      <c r="I25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="16">
         <v>1</v>
       </c>
-      <c r="K25" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="M25" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N25" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R25" s="21">
+      <c r="K25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R25" s="18">
         <v>2</v>
       </c>
-      <c r="S25" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="T25" s="21" t="s">
+      <c r="S25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="U25" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
@@ -9589,60 +9630,63 @@
       <c r="C26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="23">
         <v>35</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="24">
         <v>102</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="12">
         <v>19</v>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="23">
         <v>46</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="24">
         <v>41</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="12">
         <v>23</v>
       </c>
-      <c r="J26" s="33">
+      <c r="J26" s="23">
         <v>22</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="24">
         <v>13</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="12">
         <v>15</v>
       </c>
-      <c r="M26" s="33">
+      <c r="M26" s="23">
         <v>14</v>
       </c>
-      <c r="N26" s="30">
+      <c r="N26" s="24">
         <v>55</v>
       </c>
-      <c r="O26" s="34">
+      <c r="O26" s="12">
         <v>10</v>
       </c>
-      <c r="P26" s="34">
+      <c r="P26" s="12">
         <v>6</v>
       </c>
-      <c r="Q26" s="34">
+      <c r="Q26" s="12">
         <v>24</v>
       </c>
-      <c r="R26" s="34">
+      <c r="R26" s="12">
         <v>20</v>
       </c>
-      <c r="S26" s="34">
+      <c r="S26" s="12">
         <v>10</v>
       </c>
-      <c r="T26" s="34">
+      <c r="T26" s="12">
         <v>18</v>
       </c>
+      <c r="U26" s="12">
+        <v>21</v>
+      </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -9651,122 +9695,128 @@
       <c r="C27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="16">
         <v>28</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="17">
         <v>76</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="18">
         <v>12</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="16">
         <v>32</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="17">
         <v>30</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="18">
         <v>15</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="16">
         <v>12</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="17">
         <v>7</v>
       </c>
-      <c r="L27" s="20">
+      <c r="L27" s="18">
         <v>8</v>
       </c>
-      <c r="M27" s="18">
+      <c r="M27" s="16">
         <v>11</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="17">
         <v>31</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="18">
         <v>7</v>
       </c>
-      <c r="P27" s="20">
+      <c r="P27" s="18">
         <v>2</v>
       </c>
-      <c r="Q27" s="20">
+      <c r="Q27" s="18">
         <v>10</v>
       </c>
-      <c r="R27" s="20">
+      <c r="R27" s="18">
         <v>9</v>
       </c>
-      <c r="S27" s="20">
+      <c r="S27" s="18">
         <v>4</v>
       </c>
-      <c r="T27" s="20">
+      <c r="T27" s="18">
         <v>10</v>
       </c>
+      <c r="U27" s="18">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="16">
         <v>7</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="17">
         <v>26</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="18">
         <v>7</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="16">
         <v>14</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="17">
         <v>11</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="18">
         <v>8</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="16">
         <v>10</v>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="17">
         <v>6</v>
       </c>
-      <c r="L28" s="21">
+      <c r="L28" s="18">
         <v>7</v>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="16">
         <v>3</v>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="17">
         <v>24</v>
       </c>
-      <c r="O28" s="21">
+      <c r="O28" s="18">
         <v>3</v>
       </c>
-      <c r="P28" s="21">
+      <c r="P28" s="18">
         <v>4</v>
       </c>
-      <c r="Q28" s="21">
+      <c r="Q28" s="18">
         <v>14</v>
       </c>
-      <c r="R28" s="21">
+      <c r="R28" s="18">
         <v>11</v>
       </c>
-      <c r="S28" s="21">
+      <c r="S28" s="18">
         <v>6</v>
       </c>
-      <c r="T28" s="21">
+      <c r="T28" s="18">
         <v>8</v>
       </c>
+      <c r="U28" s="18">
+        <v>12</v>
+      </c>
     </row>
-    <row r="29" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+    <row r="29" spans="1:21" s="25" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -9775,60 +9825,63 @@
       <c r="C29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="23">
         <v>12</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="24">
         <v>1</v>
       </c>
-      <c r="F29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="29">
+      <c r="F29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="23">
         <v>14</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="24">
         <v>19</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="12">
         <v>3</v>
       </c>
-      <c r="J29" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" s="30">
+      <c r="J29" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="24">
         <v>2</v>
       </c>
-      <c r="L29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="M29" s="29">
+      <c r="L29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M29" s="23">
         <v>7</v>
       </c>
-      <c r="N29" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="O29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="P29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="R29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="S29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="T29" s="34" t="s">
+      <c r="N29" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="U29" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -9837,184 +9890,193 @@
       <c r="C30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="16">
         <v>9</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="17">
         <v>1</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G30" s="18">
+      <c r="F30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="16">
         <v>9</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="17">
         <v>11</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="18">
         <v>2</v>
       </c>
-      <c r="J30" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="M30" s="18">
+      <c r="J30" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M30" s="16">
         <v>7</v>
       </c>
-      <c r="N30" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="S30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="T30" s="20" t="s">
+      <c r="N30" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="U30" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="16">
         <v>3</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G31" s="18">
+      <c r="E31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="16">
         <v>5</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="17">
         <v>8</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="18">
         <v>1</v>
       </c>
-      <c r="J31" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="K31" s="19">
+      <c r="J31" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K31" s="17">
         <v>2</v>
       </c>
-      <c r="L31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="M31" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N31" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="S31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="T31" s="21" t="s">
+      <c r="L31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="U31" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+    <row r="32" spans="1:21" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="23">
         <v>7</v>
       </c>
-      <c r="E32" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="G32" s="29">
+      <c r="E32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="23">
         <v>6</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="24">
         <v>4</v>
       </c>
-      <c r="I32" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="J32" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="K32" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="L32" s="31">
+      <c r="I32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L32" s="24">
         <v>1</v>
       </c>
-      <c r="M32" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="N32" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="O32" s="31">
+      <c r="M32" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="N32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="O32" s="24">
         <v>1</v>
       </c>
-      <c r="P32" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q32" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="R32" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="S32" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="T32" s="31">
+      <c r="P32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="R32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="S32" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="T32" s="24">
         <v>1</v>
       </c>
+      <c r="U32" s="24">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -10023,128 +10085,134 @@
       <c r="C33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="16">
         <v>5</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33" s="18">
+      <c r="E33" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="16">
         <v>4</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="17">
         <v>2</v>
       </c>
-      <c r="I33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L33" s="20">
+      <c r="I33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L33" s="18">
         <v>1</v>
       </c>
-      <c r="M33" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N33" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O33" s="20">
+      <c r="M33" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O33" s="18">
         <v>1</v>
       </c>
-      <c r="P33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="S33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="T33" s="20">
+      <c r="P33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T33" s="18">
         <v>1</v>
       </c>
+      <c r="U33" s="18" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="19">
         <v>2</v>
       </c>
-      <c r="E34" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="22">
+      <c r="E34" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="19">
         <v>2</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="20">
         <v>2</v>
       </c>
-      <c r="I34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="J34" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="M34" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="O34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="P34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="R34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="S34" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="T34" s="24" t="s">
-        <v>48</v>
+      <c r="I34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="O34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="P34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="R34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="S34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="T34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="U34" s="21">
+        <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="6" t="s">
         <v>46</v>
       </c>
     </row>
